--- a/docs/oc-mensuales/emergencias-contingencias-y-prevencion/mar-2026.xlsx
+++ b/docs/oc-mensuales/emergencias-contingencias-y-prevencion/mar-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>18272.18</v>
+        <v>19079.11</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>495.46</v>
+        <v>517.34</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>726.73</v>
+        <v>758.83</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>8989.35</v>
+        <v>9386.33</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1431.73</v>
+        <v>1494.96</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>17978.69</v>
+        <v>18772.67</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>41910.63</v>
+        <v>43761.49</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1070.21</v>
+        <v>1117.48</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>451.5</v>
+        <v>471.44</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1136.07</v>
+        <v>1186.24</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>8298.379999999999</v>
+        <v>8664.860000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>24895.15</v>
+        <v>25994.57</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>8298.379999999999</v>
+        <v>8664.860000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>635.67</v>
+        <v>663.74</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>1400.96</v>
+        <v>1462.83</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>8854.799999999999</v>
+        <v>9245.85</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>7595.58</v>
+        <v>7931.01</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>4856.01</v>
+        <v>5070.47</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>854.8</v>
+        <v>892.55</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>294.43</v>
+        <v>307.43</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>451.5</v>
+        <v>471.44</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>2278.08</v>
+        <v>2378.68</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>262.09</v>
+        <v>273.67</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>264.68</v>
+        <v>276.37</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>15513.67</v>
+        <v>15964.28</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>2193.29</v>
+        <v>2257</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>650.01</v>
+        <v>668.89</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>8871.940000000001</v>
+        <v>9129.639999999999</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>644.3099999999999</v>
+        <v>663.02</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>8801.23</v>
+        <v>9056.879999999999</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>11381.16</v>
+        <v>11711.74</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>2278.14</v>
+        <v>2344.31</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>5171.22</v>
+        <v>5321.43</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>451.5</v>
+        <v>464.61</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>1110.77</v>
+        <v>1143.03</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>17602.46</v>
+        <v>18113.75</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>728.16</v>
+        <v>749.3099999999999</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>8854.799999999999</v>
+        <v>9112</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>546.26</v>
+        <v>562.12</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>37216.5</v>
+        <v>38297.51</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>190862.82</v>
+        <v>196406.72</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>145.25</v>
+        <v>149.47</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>8989.35</v>
+        <v>9024.790000000001</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>922.3200000000001</v>
+        <v>925.96</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>8989.35</v>
+        <v>9024.790000000001</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>668.74</v>
+        <v>671.37</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>8800.219999999999</v>
+        <v>8834.92</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>549.3</v>
+        <v>551.46</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>451.5</v>
+        <v>453.28</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>9136.09</v>
+        <v>9172.110000000001</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>696.88</v>
+        <v>699.63</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>451.5</v>
+        <v>453.28</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>24895.15</v>
+        <v>24993.3</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>16243.41</v>
+        <v>16307.46</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>474.4</v>
+        <v>476.27</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>8151.41</v>
+        <v>8183.55</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>24581.37</v>
+        <v>24678.29</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>612.28</v>
+        <v>614.6900000000001</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>8854.799999999999</v>
+        <v>9000.74</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>625.78</v>
+        <v>636.1</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>656.58</v>
+        <v>667.4</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>8854.799999999999</v>
+        <v>9000.74</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>8796.280000000001</v>
+        <v>8941.26</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>7834</v>
+        <v>7963.11</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>538.8200000000001</v>
+        <v>547.7</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>9009.57</v>
+        <v>9158.059999999999</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>538.8200000000001</v>
+        <v>547.7</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>9009.57</v>
+        <v>9158.059999999999</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>20895.78</v>
+        <v>21240.17</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>41078.71</v>
+        <v>41755.75</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>2569.19</v>
+        <v>2575.51</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>59.71</v>
+        <v>59.86</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>641.65</v>
+        <v>643.23</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>66387.07000000001</v>
+        <v>66550.41</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>52777.71</v>
+        <v>52907.56</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>6702.97</v>
+        <v>6719.46</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>451.5</v>
+        <v>452.61</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>8854.799999999999</v>
+        <v>8876.59</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>4755.2</v>
+        <v>4766.9</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>8699.51</v>
+        <v>8720.92</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>13019.85</v>
+        <v>13051.88</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>827.1799999999999</v>
+        <v>829.22</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>59.71</v>
+        <v>59.86</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>8298.379999999999</v>
+        <v>8318.799999999999</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>3677.79</v>
+        <v>3686.84</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>1208.13</v>
+        <v>1211.1</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>2579.86</v>
+        <v>2586.2</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>9009.57</v>
+        <v>9031.73</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>14120.64</v>
+        <v>14155.38</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>2104.94</v>
+        <v>2110.11</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>726.35</v>
+        <v>728.13</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>460.43</v>
+        <v>461.57</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>8854.799999999999</v>
+        <v>8876.59</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>657.63</v>
+        <v>659.25</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>1410.57</v>
+        <v>1414.04</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>2710.83</v>
+        <v>2717.5</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>8854.799999999999</v>
+        <v>8876.59</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>6569.87</v>
+        <v>6485.28</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>451.5</v>
+        <v>445.69</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>843.3200000000001</v>
+        <v>832.46</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>8381.24</v>
+        <v>8273.34</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>145.25</v>
+        <v>143.38</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>9009.57</v>
+        <v>8893.58</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>8031.22</v>
+        <v>7927.83</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>7692.85</v>
+        <v>7593.81</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>538.8200000000001</v>
+        <v>531.89</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>611.8099999999999</v>
+        <v>607.49</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>2835.79</v>
+        <v>2815.78</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>916.74</v>
+        <v>910.27</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>8298.379999999999</v>
+        <v>8239.82</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>8382.129999999999</v>
+        <v>8322.969999999999</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>2557.2</v>
+        <v>2539.15</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>7694.91</v>
+        <v>7640.61</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>163.18</v>
+        <v>162.03</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>8382.129999999999</v>
+        <v>8322.969999999999</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>10227.35</v>
+        <v>10155.18</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>10550.55</v>
+        <v>10476.09</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>5097.98</v>
+        <v>5190.41</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>14114.27</v>
+        <v>14370.17</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>699.4400000000001</v>
+        <v>712.12</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>8381.24</v>
+        <v>8533.200000000001</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>679.55</v>
+        <v>691.87</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>8369.76</v>
+        <v>8521.5</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>1102.55</v>
+        <v>1122.54</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>74685.45</v>
+        <v>75855.36</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>79166.56</v>
+        <v>80406.66</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>6882.59</v>
+        <v>6990.41</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>9968.01</v>
+        <v>10124.15</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>19855.71</v>
+        <v>20166.74</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>262.09</v>
+        <v>266.2</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>2504.26</v>
+        <v>2543.49</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>451.5</v>
+        <v>458.57</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>775.87</v>
+        <v>788.03</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>1136.07</v>
+        <v>1153.86</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>12801.81</v>
+        <v>13002.34</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>8854.799999999999</v>
+        <v>8993.51</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>690.75</v>
+        <v>701.5700000000001</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>503.88</v>
+        <v>503.86</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>9008.809999999999</v>
+        <v>9008.35</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>570.09</v>
+        <v>570.0599999999999</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>8989.35</v>
+        <v>8988.879999999999</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>138.97</v>
+        <v>138.96</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>53231.64</v>
+        <v>53228.9</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>614.11</v>
+        <v>614.08</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>8796.280000000001</v>
+        <v>8795.83</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>879.86</v>
+        <v>879.8099999999999</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>1199.2</v>
+        <v>1199.14</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>17743.88</v>
+        <v>17742.97</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>41491.92</v>
+        <v>41489.78</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>4993.09</v>
+        <v>4992.84</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>1409.04</v>
+        <v>1408.97</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>1704.31</v>
+        <v>1704.22</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>2916.32</v>
+        <v>2916.17</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>1892.05</v>
+        <v>1891.95</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>808.46</v>
+        <v>808.42</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>3497.76</v>
+        <v>3497.58</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>6970.29</v>
+        <v>6939.12</v>
       </c>
     </row>
     <row r="159">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>166.01</v>
+        <v>165.27</v>
       </c>
     </row>
     <row r="160">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>10541.24</v>
+        <v>10494.1</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>2739.17</v>
+        <v>2726.92</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>8854.799999999999</v>
+        <v>8815.209999999999</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>2575.28</v>
+        <v>2563.76</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>976.4400000000001</v>
+        <v>972.0700000000001</v>
       </c>
     </row>
     <row r="165">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>628.0700000000001</v>
+        <v>625.26</v>
       </c>
     </row>
     <row r="166">
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>8298.379999999999</v>
+        <v>8261.280000000001</v>
       </c>
     </row>
     <row r="167">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>21417.48</v>
+        <v>21321.71</v>
       </c>
     </row>
     <row r="168">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>1092.12</v>
+        <v>1087.23</v>
       </c>
     </row>
     <row r="169">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>20316.05</v>
+        <v>20225.21</v>
       </c>
     </row>
     <row r="170">
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>27028.7</v>
+        <v>26907.84</v>
       </c>
     </row>
     <row r="171">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>1122.66</v>
+        <v>1123.63</v>
       </c>
     </row>
     <row r="172">
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>17743.88</v>
+        <v>17759.17</v>
       </c>
     </row>
     <row r="173">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>538.8200000000001</v>
+        <v>539.29</v>
       </c>
     </row>
     <row r="174">
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>41491.92</v>
+        <v>41527.66</v>
       </c>
     </row>
     <row r="175">
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>9009.57</v>
+        <v>9017.33</v>
       </c>
     </row>
     <row r="176">
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>462.03</v>
+        <v>462.43</v>
       </c>
     </row>
     <row r="177">
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>8872.120000000001</v>
+        <v>8879.76</v>
       </c>
     </row>
     <row r="178">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>8506.23</v>
+        <v>8513.559999999999</v>
       </c>
     </row>
     <row r="179">
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>8744.52</v>
+        <v>8752.049999999999</v>
       </c>
     </row>
     <row r="180">
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>35185.14</v>
+        <v>35215.45</v>
       </c>
     </row>
     <row r="181">
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>2668.01</v>
+        <v>2679.03</v>
       </c>
     </row>
     <row r="182">
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>54831.17</v>
+        <v>55057.67</v>
       </c>
     </row>
     <row r="183">
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>2476.38</v>
+        <v>2469.55</v>
       </c>
     </row>
     <row r="184">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>3233.13</v>
+        <v>3224.21</v>
       </c>
     </row>
     <row r="185">
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>1460.21</v>
+        <v>1456.18</v>
       </c>
     </row>
     <row r="186">
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>865.35</v>
+        <v>862.96</v>
       </c>
     </row>
     <row r="187">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>1376.99</v>
+        <v>1373.19</v>
       </c>
     </row>
     <row r="188">
@@ -11915,7 +11915,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>8801.23</v>
+        <v>8776.950000000001</v>
       </c>
     </row>
     <row r="189">
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>903</v>
+        <v>900.51</v>
       </c>
     </row>
     <row r="190">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>657.63</v>
+        <v>655.8099999999999</v>
       </c>
     </row>
     <row r="191">
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>5024.91</v>
+        <v>5011.05</v>
       </c>
     </row>
     <row r="192">
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>1453.89</v>
+        <v>1449.88</v>
       </c>
     </row>
     <row r="193">
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>1291.55</v>
+        <v>1287.99</v>
       </c>
     </row>
     <row r="194">
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>8854.799999999999</v>
+        <v>8830.379999999999</v>
       </c>
     </row>
     <row r="195">
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>728.15</v>
+        <v>726.14</v>
       </c>
     </row>
     <row r="196">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>8854.799999999999</v>
+        <v>8830.379999999999</v>
       </c>
     </row>
     <row r="197">
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>8298.379999999999</v>
+        <v>8275.49</v>
       </c>
     </row>
     <row r="198">
@@ -12525,7 +12525,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>495.53</v>
+        <v>494.16</v>
       </c>
     </row>
     <row r="199">
@@ -12586,7 +12586,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>8381.24</v>
+        <v>8358.120000000001</v>
       </c>
     </row>
     <row r="200">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>7900.7</v>
+        <v>7878.91</v>
       </c>
     </row>
     <row r="201">
@@ -12708,7 +12708,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>17600.6</v>
+        <v>17397.41</v>
       </c>
     </row>
     <row r="202">
@@ -12769,7 +12769,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>547.54</v>
+        <v>541.22</v>
       </c>
     </row>
     <row r="203">
@@ -12830,7 +12830,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>8800.299999999999</v>
+        <v>8698.709999999999</v>
       </c>
     </row>
     <row r="204">
@@ -12891,7 +12891,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>8298.379999999999</v>
+        <v>8202.58</v>
       </c>
     </row>
     <row r="205">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>9532.66</v>
+        <v>9422.610000000001</v>
       </c>
     </row>
     <row r="206">
@@ -13013,7 +13013,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>776.78</v>
+        <v>767.8099999999999</v>
       </c>
     </row>
     <row r="207">
@@ -13074,7 +13074,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>8800.299999999999</v>
+        <v>8698.709999999999</v>
       </c>
     </row>
     <row r="208">
@@ -13135,7 +13135,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>290.11</v>
+        <v>286.76</v>
       </c>
     </row>
     <row r="209">
@@ -13196,7 +13196,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>198.63</v>
+        <v>196.34</v>
       </c>
     </row>
     <row r="210">
@@ -13257,7 +13257,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>8298.379999999999</v>
+        <v>8202.58</v>
       </c>
     </row>
     <row r="211">
@@ -13318,7 +13318,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>2500.31</v>
+        <v>2463.02</v>
       </c>
     </row>
     <row r="212">
@@ -13379,7 +13379,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>2058.52</v>
+        <v>2027.81</v>
       </c>
     </row>
     <row r="213">
@@ -13440,7 +13440,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>19346.22</v>
+        <v>19057.66</v>
       </c>
     </row>
     <row r="214">
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>1444.83</v>
+        <v>1423.28</v>
       </c>
     </row>
     <row r="215">
@@ -13562,7 +13562,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>7690</v>
+        <v>7575.3</v>
       </c>
     </row>
     <row r="216">
@@ -13623,7 +13623,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>651.61</v>
+        <v>641.89</v>
       </c>
     </row>
     <row r="217">
@@ -13684,7 +13684,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>2005.54</v>
+        <v>1975.63</v>
       </c>
     </row>
     <row r="218">
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>3520.62</v>
+        <v>3500.39</v>
       </c>
     </row>
     <row r="219">
@@ -13806,7 +13806,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>36112.59</v>
+        <v>35905.15</v>
       </c>
     </row>
     <row r="220">
@@ -13867,7 +13867,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>223.9</v>
+        <v>222.62</v>
       </c>
     </row>
     <row r="221">
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>17709.61</v>
+        <v>17607.88</v>
       </c>
     </row>
     <row r="222">
@@ -13989,7 +13989,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>1628.86</v>
+        <v>1619.51</v>
       </c>
     </row>
     <row r="223">
@@ -14050,7 +14050,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>4115.14</v>
+        <v>4091.5</v>
       </c>
     </row>
     <row r="224">
@@ -14111,7 +14111,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>10863.88</v>
+        <v>10801.48</v>
       </c>
     </row>
     <row r="225">
@@ -14172,7 +14172,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>451.8</v>
+        <v>449.21</v>
       </c>
     </row>
     <row r="226">
@@ -14233,7 +14233,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>18017.63</v>
+        <v>17914.13</v>
       </c>
     </row>
     <row r="227">
@@ -14294,7 +14294,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>1145.62</v>
+        <v>1139.04</v>
       </c>
     </row>
     <row r="228">
@@ -14355,7 +14355,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>772.15</v>
+        <v>767.21</v>
       </c>
     </row>
     <row r="229">
@@ -14416,7 +14416,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>6802.12</v>
+        <v>6758.54</v>
       </c>
     </row>
     <row r="230">
@@ -14477,7 +14477,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>330.23</v>
+        <v>328.12</v>
       </c>
     </row>
     <row r="231">
@@ -14538,7 +14538,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>264.68</v>
+        <v>263.54</v>
       </c>
     </row>
     <row r="232">
@@ -14599,7 +14599,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>657.27</v>
+        <v>654.4400000000001</v>
       </c>
     </row>
     <row r="233">
@@ -14660,7 +14660,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>8800.299999999999</v>
+        <v>8762.389999999999</v>
       </c>
     </row>
     <row r="234">
@@ -14721,7 +14721,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>1310.93</v>
+        <v>1305.28</v>
       </c>
     </row>
     <row r="235">
@@ -14782,7 +14782,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>353.17</v>
+        <v>351.64</v>
       </c>
     </row>
     <row r="236">
@@ -14843,7 +14843,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>21841.02</v>
+        <v>21746.93</v>
       </c>
     </row>
     <row r="237">
@@ -14904,7 +14904,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>18102.76</v>
+        <v>17840.87</v>
       </c>
     </row>
     <row r="238">
@@ -14965,7 +14965,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>1937.29</v>
+        <v>1909.26</v>
       </c>
     </row>
     <row r="239">
@@ -15026,7 +15026,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>538.8200000000001</v>
+        <v>531.03</v>
       </c>
     </row>
     <row r="240">
@@ -15087,7 +15087,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>9220.309999999999</v>
+        <v>9086.92</v>
       </c>
     </row>
     <row r="241">
@@ -15148,7 +15148,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>6583.51</v>
+        <v>6488.27</v>
       </c>
     </row>
     <row r="242">
@@ -15209,7 +15209,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>254.74</v>
+        <v>251.05</v>
       </c>
     </row>
     <row r="243">
@@ -15270,7 +15270,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>1059.5</v>
+        <v>1044.17</v>
       </c>
     </row>
     <row r="244">
@@ -15331,7 +15331,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>8641.139999999999</v>
+        <v>8516.129999999999</v>
       </c>
     </row>
     <row r="245">
@@ -15392,7 +15392,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>9009.57</v>
+        <v>8879.219999999999</v>
       </c>
     </row>
     <row r="246">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>9304.120000000001</v>
+        <v>9103.950000000001</v>
       </c>
     </row>
     <row r="247">
@@ -15514,7 +15514,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>32527.43</v>
+        <v>31827.61</v>
       </c>
     </row>
     <row r="248">
@@ -15575,7 +15575,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>560.64</v>
+        <v>548.58</v>
       </c>
     </row>
     <row r="249">
@@ -15636,7 +15636,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>658.4299999999999</v>
+        <v>644.27</v>
       </c>
     </row>
     <row r="250">
@@ -15697,7 +15697,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>493.4</v>
+        <v>482.79</v>
       </c>
     </row>
     <row r="251">
@@ -15758,7 +15758,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>493.4</v>
+        <v>482.79</v>
       </c>
     </row>
     <row r="252">
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>2648.99</v>
+        <v>2592</v>
       </c>
     </row>
     <row r="253">
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>2496.61</v>
+        <v>2442.9</v>
       </c>
     </row>
     <row r="254">
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>18434.61</v>
+        <v>18037.99</v>
       </c>
     </row>
     <row r="255">
@@ -16002,7 +16002,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>2315.51</v>
+        <v>2265.69</v>
       </c>
     </row>
     <row r="256">
@@ -16063,7 +16063,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>461.94</v>
+        <v>452</v>
       </c>
     </row>
     <row r="257">
@@ -16124,7 +16124,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>8800.299999999999</v>
+        <v>8610.959999999999</v>
       </c>
     </row>
     <row r="258">
@@ -16185,7 +16185,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>9304.120000000001</v>
+        <v>9103.950000000001</v>
       </c>
     </row>
     <row r="259">
@@ -16246,7 +16246,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>8854.799999999999</v>
+        <v>8648.76</v>
       </c>
     </row>
     <row r="260">
@@ -16307,7 +16307,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>1096.24</v>
+        <v>1070.73</v>
       </c>
     </row>
     <row r="261">
@@ -16368,7 +16368,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>728.16</v>
+        <v>711.21</v>
       </c>
     </row>
     <row r="262">
@@ -16429,7 +16429,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>1075.61</v>
+        <v>1050.58</v>
       </c>
     </row>
     <row r="263">
@@ -16490,7 +16490,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>1174.38</v>
+        <v>1147.05</v>
       </c>
     </row>
     <row r="264">
@@ -16551,7 +16551,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>15477.64</v>
+        <v>15117.48</v>
       </c>
     </row>
     <row r="265">
@@ -16612,7 +16612,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>1926.9</v>
+        <v>1882.06</v>
       </c>
     </row>
     <row r="266">
@@ -16673,7 +16673,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>1491.93</v>
+        <v>1457.21</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/emergencias-contingencias-y-prevencion/mar-2026.xlsx
+++ b/docs/oc-mensuales/emergencias-contingencias-y-prevencion/mar-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC mar-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC mar-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -14091,7 +14091,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -16470,7 +16470,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -16531,7 +16531,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">

--- a/docs/oc-mensuales/emergencias-contingencias-y-prevencion/mar-2026.xlsx
+++ b/docs/oc-mensuales/emergencias-contingencias-y-prevencion/mar-2026.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>SUPERMERCADO MAYORISTA METROPOLITANO</t>
+          <t>supermercado mayorista metropolitano</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3045,7 +3045,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6644,7 +6644,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7437,7 +7437,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILPUE</t>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7925,7 +7925,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8047,7 +8047,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8108,7 +8108,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8169,7 +8169,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -8230,7 +8230,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8352,7 +8352,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8657,7 +8657,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ALAMOS</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8779,7 +8779,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8901,7 +8901,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8962,7 +8962,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -9023,7 +9023,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9084,7 +9084,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9145,7 +9145,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9206,7 +9206,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9216,7 +9216,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9318,7 +9318,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9338,7 +9338,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -9389,7 +9389,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9450,7 +9450,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9521,7 +9521,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -9572,7 +9572,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9938,7 +9938,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Regimiento Reforzado N° 1 "Calama"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -9999,7 +9999,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Regimiento Reforzado N° 1 "Calama"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10060,7 +10060,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10192,7 +10192,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>SUPERMERCADO MAYORISTA METROPOLITANO</t>
+          <t>supermercado mayorista metropolitano</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -10243,7 +10243,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10365,7 +10365,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10548,7 +10548,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10731,7 +10731,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Metropolitana</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -10853,7 +10853,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -10924,7 +10924,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -10975,7 +10975,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11036,7 +11036,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11097,7 +11097,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11158,7 +11158,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11402,7 +11402,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11412,7 +11412,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -11585,7 +11585,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11707,7 +11707,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -11768,7 +11768,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -11829,7 +11829,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -11900,7 +11900,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -11951,7 +11951,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -12012,7 +12012,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12073,7 +12073,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12134,7 +12134,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12256,7 +12256,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -12317,7 +12317,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -12378,7 +12378,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12439,7 +12439,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -12500,7 +12500,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -12561,7 +12561,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -12622,7 +12622,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -12683,7 +12683,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -12693,7 +12693,7 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -12805,7 +12805,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -12815,7 +12815,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -12866,7 +12866,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -12927,7 +12927,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -12988,7 +12988,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13049,7 +13049,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13059,7 +13059,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -13110,7 +13110,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -13171,7 +13171,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13232,7 +13232,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13293,7 +13293,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -13354,7 +13354,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -13415,7 +13415,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -13598,7 +13598,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -13659,7 +13659,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -13720,7 +13720,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -13842,7 +13842,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -13903,7 +13903,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -13964,7 +13964,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -14025,7 +14025,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14147,7 +14147,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -14208,7 +14208,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -14269,7 +14269,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -14452,7 +14452,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE CASABLANCA</t>
+          <t>I MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -14513,7 +14513,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -14635,7 +14635,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -14645,7 +14645,7 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -14696,7 +14696,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -14940,7 +14940,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -15001,7 +15001,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -15123,7 +15123,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -15184,7 +15184,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -15245,7 +15245,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -15306,7 +15306,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -15367,7 +15367,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -15428,7 +15428,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -15550,7 +15550,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -15611,7 +15611,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -15672,7 +15672,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -15733,7 +15733,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -15794,7 +15794,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -15916,7 +15916,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -15977,7 +15977,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -16038,7 +16038,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -16099,7 +16099,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -16109,7 +16109,7 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
@@ -16160,7 +16160,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -16221,7 +16221,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -16282,7 +16282,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -16343,7 +16343,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -16587,7 +16587,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE D</t>
+          <t>SERVICIO NACIONAL DE PREVENCIÓN Y RESPUESTA ANTE DESASTRES</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">

--- a/docs/oc-mensuales/emergencias-contingencias-y-prevencion/mar-2026.xlsx
+++ b/docs/oc-mensuales/emergencias-contingencias-y-prevencion/mar-2026.xlsx
@@ -623,7 +623,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +814,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1123,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1371,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1436,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1562,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1688,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1753,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1879,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2188,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2314,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2440,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2505,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2692,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2818,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +2944,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3253,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3501,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +3932,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +3997,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4062,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4127,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4497,11 @@
           <t>76.102.347-0</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4562,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4688,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +4936,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5062,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5432,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5497,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +5867,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +5932,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6058,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6611,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +6981,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7046,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7111,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7176,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7241,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7550,11 @@
           <t>76.287.511-k</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7638,7 +7798,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +7863,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8477,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +8786,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +8851,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +8916,11 @@
           <t>76.712.337-K</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +9042,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9107,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9233,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9359,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9485,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9407,7 +9611,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +9676,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +9924,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10111,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10139,7 +10359,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10444,7 +10668,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10505,7 +10733,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10627,7 +10859,11 @@
           <t>77.721.492-6</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10688,7 +10924,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11176,7 +11416,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +11542,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11359,7 +11607,11 @@
           <t>77.544.929-2</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11481,7 +11733,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11664,7 +11920,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12091,7 +12351,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13555,7 +13819,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13799,7 +14067,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14104,7 +14376,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14348,7 +14624,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14409,7 +14689,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14470,7 +14754,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14592,7 +14880,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14836,7 +15128,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14897,7 +15193,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15080,7 +15380,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15507,7 +15811,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15690,7 +15998,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15751,7 +16063,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15812,7 +16128,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16300,7 +16620,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16361,7 +16685,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16422,7 +16750,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16544,7 +16876,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16605,7 +16941,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16666,7 +17006,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/emergencias-contingencias-y-prevencion/mar-2026.xlsx
+++ b/docs/oc-mensuales/emergencias-contingencias-y-prevencion/mar-2026.xlsx
@@ -4725,7 +4725,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
